--- a/prediction_model/var_combinations.xlsx
+++ b/prediction_model/var_combinations.xlsx
@@ -9542,7 +9542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9615,11 +9615,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Flachdach ungedämmt</t>
+          <t>Konventioneller mit BH</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -9630,11 +9630,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Konventioneller mit BH</t>
+          <t>Konventioneller ohne BH</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
@@ -9645,26 +9645,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Konventioneller ohne BH</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>Mineraldämmung oder leichte Dämmelemente</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>Konventioneller mit BH</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -9675,11 +9675,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Konventioneller mit BH</t>
+          <t>Konventioneller ohne BH</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -9690,25 +9690,10 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Konventioneller ohne BH</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mineraldämmung oder leichte Dämmelemente</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14685,7 +14670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14762,7 +14747,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6">
@@ -14793,21 +14778,6 @@
       </c>
       <c r="C7" t="n">
         <v>57</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Flachdach ungedämmt</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>vor_1990</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -14821,7 +14791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14883,7 +14853,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5">
@@ -14959,21 +14929,6 @@
       </c>
       <c r="C9" t="n">
         <v>114</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Flachdach ungedämmt</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1901-1950</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -14987,7 +14942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15120,11 +15075,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Massiv Holz</t>
+          <t>Massivbau</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -15169,7 +15124,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -15180,11 +15135,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Massivbau</t>
+          <t>Massiv Holz</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>286</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -15240,11 +15195,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Leichtbau</t>
+          <t>Massiv Backstein</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -15360,26 +15315,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Massiv Backstein</t>
+          <t>Leichtbau</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Flachdach ungedämmt</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Punktuell Beton mit Backsteinwänden</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15749,7 +15689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15841,7 +15781,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
@@ -15902,21 +15842,6 @@
       </c>
       <c r="C10" t="n">
         <v>125</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Flachdach ungedämmt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15930,7 +15855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16052,7 +15977,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -16123,7 +16048,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zweischalenmauerwerk, Holz aussen</t>
+          <t>Leichtbau Glasfasernplatte</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -16153,11 +16078,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zweischalenmauerwerk, Beton aussen</t>
+          <t>Beton, Holz ungedämmt</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -16168,11 +16093,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Beton, Holz ungedämmt</t>
+          <t>Zweischalenmauerwerk, Beton aussen</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -16333,25 +16258,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Leichtbau Glasfasernplatte</t>
+          <t>Zweischalenmauerwerk, Holz aussen</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Flachdach ungedämmt</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Massiv Backstein mit hinterlüftung</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16366,7 +16276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16473,7 +16383,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8">
@@ -16519,21 +16429,6 @@
       </c>
       <c r="C10" t="n">
         <v>53</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Flachdach ungedämmt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>VOR_1990</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
